--- a/Figures/pairwise_adonis_21_same_sheet.xlsx
+++ b/Figures/pairwise_adonis_21_same_sheet.xlsx
@@ -416,7 +416,7 @@
         <v>1.20273826429406</v>
       </c>
       <c r="E6" t="n">
-        <v>0.351</v>
+        <v>0.359</v>
       </c>
     </row>
     <row r="7">
@@ -481,7 +481,7 @@
         <v>0.897454008755927</v>
       </c>
       <c r="E12" t="n">
-        <v>0.47</v>
+        <v>0.447</v>
       </c>
     </row>
     <row r="13">
@@ -546,7 +546,7 @@
         <v>0.213393748091386</v>
       </c>
       <c r="E18" t="n">
-        <v>0.993</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="19">
